--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R2025c51499764631"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R56ed97af72a446ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rad528434fbec4104"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rb5617ec1cc1d4d08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rcf464f77cd904a2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rb1ae3445deeb467e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rc79679dc53014954"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R9047c15f36a54289"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R9ea0dbb6ca394e76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R22c6b317d2664d4c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -320,7 +320,7 @@
         <x:v>交付物名称</x:v>
       </x:c>
       <x:c r="B1" s="9" t="str">
-        <x:v>固定路径或命名规则</x:v>
+        <x:v>固定路径/命名规则</x:v>
       </x:c>
       <x:c r="C1" s="9" t="str">
         <x:v>格式</x:v>
